--- a/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007</t>
+          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252382</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267920</t>
+          <t>267814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244442</t>
+          <t>244221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257994</t>
+          <t>258126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503494</t>
+          <t>503871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523009</t>
+          <t>523245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28957</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52373</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84902</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454762</t>
+          <t>453588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>474846</t>
+          <t>474436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451576</t>
+          <t>450038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474992</t>
+          <t>474801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912122</t>
+          <t>910959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944384</t>
+          <t>944891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35806</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62102</t>
+          <t>61703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283040</t>
+          <t>282843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304058</t>
+          <t>302552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302264</t>
+          <t>301811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320935</t>
+          <t>321489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592156</t>
+          <t>592555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>620072</t>
+          <t>620755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32415</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339802</t>
+          <t>340624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354234</t>
+          <t>354138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348725</t>
+          <t>350038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364351</t>
+          <t>364498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696654</t>
+          <t>696695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716433</t>
+          <t>715338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>27165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185765</t>
+          <t>184804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197195</t>
+          <t>197324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182184</t>
+          <t>181985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196081</t>
+          <t>196469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374594</t>
+          <t>374482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391860</t>
+          <t>391485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257032</t>
+          <t>256967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268739</t>
+          <t>268033</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262061</t>
+          <t>261319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274069</t>
+          <t>273336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525609</t>
+          <t>525529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540225</t>
+          <t>541089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45027</t>
+          <t>43922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41599</t>
+          <t>41951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72960</t>
+          <t>73683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66954</t>
+          <t>69366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106467</t>
+          <t>106814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>569014</t>
+          <t>570119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>592300</t>
+          <t>592924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>565259</t>
+          <t>564536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596620</t>
+          <t>596268</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1145793</t>
+          <t>1145446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1185306</t>
+          <t>1182894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>31893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57342</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57588</t>
+          <t>56271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68079</t>
+          <t>69139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104756</t>
+          <t>106637</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>682507</t>
+          <t>683593</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>707961</t>
+          <t>707956</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>722925</t>
+          <t>724242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750211</t>
+          <t>749787</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1415605</t>
+          <t>1413724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1452282</t>
+          <t>1451222</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>183004</t>
+          <t>187136</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>232663</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322844</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>400050</t>
+          <t>399602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3083118</t>
+          <t>3078986</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3134102</t>
+          <t>3132178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3137619</t>
+          <t>3138991</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3196098</t>
+          <t>3196962</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6236354</t>
+          <t>6236802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6313560</t>
+          <t>6313260</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012</t>
+          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>31788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>31777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31775</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57343</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260519</t>
+          <t>260821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279087</t>
+          <t>278966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250555</t>
+          <t>251232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268962</t>
+          <t>270032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518275</t>
+          <t>516212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543843</t>
+          <t>543963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>49591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40679</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48798</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80822</t>
+          <t>81514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454783</t>
+          <t>453893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477937</t>
+          <t>478987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479007</t>
+          <t>480054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500319</t>
+          <t>500537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>942348</t>
+          <t>941656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974372</t>
+          <t>973212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304929</t>
+          <t>304586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318147</t>
+          <t>317448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315475</t>
+          <t>316126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332902</t>
+          <t>332750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626410</t>
+          <t>626658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647550</t>
+          <t>647025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40080</t>
+          <t>41533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343889</t>
+          <t>344043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359530</t>
+          <t>360067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365209</t>
+          <t>365284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379806</t>
+          <t>379668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715558</t>
+          <t>714105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736181</t>
+          <t>735619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,82 +5443,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13378</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7621</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21608</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>21527</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>13924</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>31248</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>7,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13378</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21215</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>21527</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>13945</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>32040</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197244</t>
+          <t>197201</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208596</t>
+          <t>209352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,82 +5556,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>206213</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>197983</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>211970</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>410682</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>400961</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>418285</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>92,77%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>206213</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>198376</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>212090</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>410682</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>400169</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>418264</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261732</t>
+          <t>262665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272012</t>
+          <t>272005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260575</t>
+          <t>260455</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273249</t>
+          <t>273183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527833</t>
+          <t>527439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543771</t>
+          <t>543194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>44188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>50450</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81104</t>
+          <t>81217</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77068</t>
+          <t>75937</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117413</t>
+          <t>114798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616067</t>
+          <t>615292</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638614</t>
+          <t>639189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>610676</t>
+          <t>610563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>642257</t>
+          <t>641330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233847</t>
+          <t>1236462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1274192</t>
+          <t>1275323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>23616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>46484</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69774</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>69517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>108746</t>
+          <t>108067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>731762</t>
+          <t>732614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>755000</t>
+          <t>755482</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>753002</t>
+          <t>755429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>782623</t>
+          <t>783006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1493129</t>
+          <t>1493808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1530938</t>
+          <t>1532358</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140369</t>
+          <t>137796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>193221</t>
+          <t>188694</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192329</t>
+          <t>190703</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>250007</t>
+          <t>249600</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>342485</t>
+          <t>348380</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>421320</t>
+          <t>421226</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3220899</t>
+          <t>3225426</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3273751</t>
+          <t>3276324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3293674</t>
+          <t>3294081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3351352</t>
+          <t>3352978</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6536481</t>
+          <t>6536575</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6615316</t>
+          <t>6609421</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016</t>
+          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33984</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34876</t>
+          <t>34428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65213</t>
+          <t>62593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256137</t>
+          <t>255488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276000</t>
+          <t>277660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252457</t>
+          <t>252255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270996</t>
+          <t>271234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514002</t>
+          <t>516622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544339</t>
+          <t>544787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47794</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>25380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48314</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53916</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86979</t>
+          <t>88563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>452900</t>
+          <t>451366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476300</t>
+          <t>476067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474770</t>
+          <t>475121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499817</t>
+          <t>497704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936799</t>
+          <t>935215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>969862</t>
+          <t>967982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302116</t>
+          <t>302107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312086</t>
+          <t>312146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305415</t>
+          <t>306247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320592</t>
+          <t>320608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613922</t>
+          <t>613116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630191</t>
+          <t>630202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>42684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>32712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>38318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65672</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326358</t>
+          <t>325625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348095</t>
+          <t>348119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356439</t>
+          <t>354571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374580</t>
+          <t>373463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689920</t>
+          <t>685570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719394</t>
+          <t>717274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196620</t>
+          <t>197141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206518</t>
+          <t>206942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203869</t>
+          <t>204014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214160</t>
+          <t>214125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405424</t>
+          <t>405971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419645</t>
+          <t>419541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255158</t>
+          <t>255212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262160</t>
+          <t>262159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265695</t>
+          <t>266609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524900</t>
+          <t>525140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533487</t>
+          <t>533546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32461</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34301</t>
+          <t>32945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>61402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617811</t>
+          <t>617460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>637378</t>
+          <t>638132</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647493</t>
+          <t>648007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668777</t>
+          <t>668957</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1274667</t>
+          <t>1275079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1302180</t>
+          <t>1303536</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34107</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>23005</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45341</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39995</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>73039</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742628</t>
+          <t>744131</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762326</t>
+          <t>763667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>779667</t>
+          <t>778348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>801766</t>
+          <t>802003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1531385</t>
+          <t>1528704</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1561748</t>
+          <t>1559749</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>122364</t>
+          <t>121449</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>171312</t>
+          <t>167990</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>136608</t>
+          <t>138065</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188378</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>270888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>340004</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3203692</t>
+          <t>3207014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3252640</t>
+          <t>3253555</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3337833</t>
+          <t>3336364</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3389603</t>
+          <t>3388146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6561212</t>
+          <t>6561321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6630518</t>
+          <t>6630328</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023</t>
+          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>32257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309439</t>
+          <t>309601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311116</t>
+          <t>311121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258689</t>
+          <t>259977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285296</t>
+          <t>285553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567265</t>
+          <t>568820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595922</t>
+          <t>596396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>44353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64235</t>
+          <t>62882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471870</t>
+          <t>472884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502078</t>
+          <t>502209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485837</t>
+          <t>486834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501875</t>
+          <t>502685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965409</t>
+          <t>966762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1000983</t>
+          <t>1001342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39345</t>
+          <t>39375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280671</t>
+          <t>281564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297659</t>
+          <t>297284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314234</t>
+          <t>314861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329791</t>
+          <t>329526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602698</t>
+          <t>602668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623886</t>
+          <t>624958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310581</t>
+          <t>310680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463776</t>
+          <t>463991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472377</t>
+          <t>472397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>775044</t>
+          <t>776180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783900</t>
+          <t>783838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249042</t>
+          <t>249889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258296</t>
+          <t>258282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426629</t>
+          <t>427259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>436967</t>
+          <t>436933</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258203</t>
+          <t>258452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266272</t>
+          <t>266295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245701</t>
+          <t>245293</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254717</t>
+          <t>254728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507633</t>
+          <t>507811</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519715</t>
+          <t>519491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33984</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>43886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71314</t>
+          <t>71743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>582642</t>
+          <t>580691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600939</t>
+          <t>600589</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>797548</t>
+          <t>798220</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>828742</t>
+          <t>829539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1387418</t>
+          <t>1386989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1425253</t>
+          <t>1426330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906076</t>
+          <t>906040</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>921272</t>
+          <t>920833</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690596</t>
+          <t>690551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701052</t>
+          <t>701615</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1603043</t>
+          <t>1602247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1621035</t>
+          <t>1621319</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>56103</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105425</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114945</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>137769</t>
+          <t>136957</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201908</t>
+          <t>201799</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3327070</t>
+          <t>3332304</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3375859</t>
+          <t>3376392</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3562794</t>
+          <t>3563730</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3607149</t>
+          <t>3608322</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6908326</t>
+          <t>6908435</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6972465</t>
+          <t>6973277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252352</t>
+          <t>252882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267814</t>
+          <t>267671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244221</t>
+          <t>244935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258126</t>
+          <t>258100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503871</t>
+          <t>503886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523245</t>
+          <t>522984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>40436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29148</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53911</t>
+          <t>53333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>53686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86065</t>
+          <t>84629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453588</t>
+          <t>452639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>474436</t>
+          <t>473781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450038</t>
+          <t>450616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474801</t>
+          <t>473686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>910959</t>
+          <t>912395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944891</t>
+          <t>943338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>34118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61703</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282843</t>
+          <t>282945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302552</t>
+          <t>303423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301811</t>
+          <t>302375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321489</t>
+          <t>321099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592555</t>
+          <t>592486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>620755</t>
+          <t>620140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32374</t>
+          <t>33818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340624</t>
+          <t>340197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354138</t>
+          <t>353620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350038</t>
+          <t>349403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364498</t>
+          <t>364167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696695</t>
+          <t>695251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715338</t>
+          <t>715016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184804</t>
+          <t>185650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197324</t>
+          <t>197160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181985</t>
+          <t>182853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196469</t>
+          <t>196479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374482</t>
+          <t>373753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391485</t>
+          <t>391439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256967</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268033</t>
+          <t>268048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261319</t>
+          <t>262470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273336</t>
+          <t>274106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525529</t>
+          <t>524805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>541089</t>
+          <t>540206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43922</t>
+          <t>44500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73683</t>
+          <t>71764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69366</t>
+          <t>65407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106814</t>
+          <t>104872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570119</t>
+          <t>569541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>592924</t>
+          <t>592083</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>564536</t>
+          <t>566455</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596268</t>
+          <t>596676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1145446</t>
+          <t>1147388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1182894</t>
+          <t>1186853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>58135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30726</t>
+          <t>30469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56271</t>
+          <t>56546</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69139</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106637</t>
+          <t>104780</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>683593</t>
+          <t>681714</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>707956</t>
+          <t>708209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>724242</t>
+          <t>723967</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>749787</t>
+          <t>750044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1413724</t>
+          <t>1415581</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1451222</t>
+          <t>1451442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>133944</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187136</t>
+          <t>185742</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>173320</t>
+          <t>174603</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>231291</t>
+          <t>230064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>319328</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399602</t>
+          <t>394110</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3078986</t>
+          <t>3080380</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3132178</t>
+          <t>3133008</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3138991</t>
+          <t>3140218</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3196962</t>
+          <t>3195679</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6236802</t>
+          <t>6242294</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6313260</t>
+          <t>6317076</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31777</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>31588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>58164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260821</t>
+          <t>259996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278966</t>
+          <t>278572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251232</t>
+          <t>251686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270032</t>
+          <t>269792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516212</t>
+          <t>517454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543963</t>
+          <t>544030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39632</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49958</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81514</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453893</t>
+          <t>453823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478987</t>
+          <t>478952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480054</t>
+          <t>478902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500537</t>
+          <t>499371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>941656</t>
+          <t>941591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973212</t>
+          <t>974862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304586</t>
+          <t>303973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317448</t>
+          <t>318230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316126</t>
+          <t>315506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332750</t>
+          <t>331932</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626658</t>
+          <t>626469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647025</t>
+          <t>647193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344043</t>
+          <t>343147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360067</t>
+          <t>360019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365284</t>
+          <t>363865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379668</t>
+          <t>379517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>714105</t>
+          <t>714727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>735619</t>
+          <t>736222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>14343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31248</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197201</t>
+          <t>197519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209352</t>
+          <t>209092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197983</t>
+          <t>198291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211970</t>
+          <t>211797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400961</t>
+          <t>401197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418285</t>
+          <t>417866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262665</t>
+          <t>262566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272005</t>
+          <t>271999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260455</t>
+          <t>261315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273183</t>
+          <t>273240</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527439</t>
+          <t>527912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543194</t>
+          <t>543310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>49273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81217</t>
+          <t>80269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75937</t>
+          <t>77111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114798</t>
+          <t>115747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>615292</t>
+          <t>616214</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639189</t>
+          <t>639254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>610563</t>
+          <t>611511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>641330</t>
+          <t>642507</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1236462</t>
+          <t>1235513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1275323</t>
+          <t>1274149</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23616</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39770</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67347</t>
+          <t>68840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69517</t>
+          <t>70020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>108067</t>
+          <t>108181</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>732614</t>
+          <t>731268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>755482</t>
+          <t>755598</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755429</t>
+          <t>753936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>783006</t>
+          <t>782925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1493808</t>
+          <t>1493694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532358</t>
+          <t>1531855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>137796</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188694</t>
+          <t>188220</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190703</t>
+          <t>193119</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>249600</t>
+          <t>250564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>348380</t>
+          <t>344656</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>421226</t>
+          <t>421901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3225426</t>
+          <t>3225900</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3276324</t>
+          <t>3274159</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3294081</t>
+          <t>3293117</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3352978</t>
+          <t>3350562</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6536575</t>
+          <t>6535900</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6609421</t>
+          <t>6613145</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37286</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>34094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34428</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62593</t>
+          <t>64601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255488</t>
+          <t>255963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277660</t>
+          <t>276818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252255</t>
+          <t>252347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271234</t>
+          <t>270910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516622</t>
+          <t>514614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544787</t>
+          <t>543940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24627</t>
+          <t>24178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>48035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55796</t>
+          <t>54576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88563</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>451366</t>
+          <t>452518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476067</t>
+          <t>476516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475121</t>
+          <t>475049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497704</t>
+          <t>498630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935215</t>
+          <t>935571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>967982</t>
+          <t>969202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302107</t>
+          <t>301612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312146</t>
+          <t>312125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306247</t>
+          <t>305733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320608</t>
+          <t>320035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613116</t>
+          <t>613711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630202</t>
+          <t>630278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>42992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38318</t>
+          <t>36487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325625</t>
+          <t>325317</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348119</t>
+          <t>348631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>354571</t>
+          <t>355839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>373463</t>
+          <t>374566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>685570</t>
+          <t>690587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717274</t>
+          <t>719105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197141</t>
+          <t>197396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206942</t>
+          <t>207295</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204014</t>
+          <t>203937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214125</t>
+          <t>214116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405971</t>
+          <t>404989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419541</t>
+          <t>419412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255212</t>
+          <t>255169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262159</t>
+          <t>262178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266609</t>
+          <t>266059</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525140</t>
+          <t>525170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533546</t>
+          <t>533476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38202</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32945</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61402</t>
+          <t>60541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617460</t>
+          <t>619077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638132</t>
+          <t>637958</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>648007</t>
+          <t>646742</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668957</t>
+          <t>669079</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275079</t>
+          <t>1275940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1303536</t>
+          <t>1303012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32604</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46660</t>
+          <t>46309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>39515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744131</t>
+          <t>743224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763667</t>
+          <t>763076</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>778348</t>
+          <t>778699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>802003</t>
+          <t>801958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1528704</t>
+          <t>1530455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1559749</t>
+          <t>1562228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>121449</t>
+          <t>121365</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167990</t>
+          <t>171510</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>138065</t>
+          <t>135844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189847</t>
+          <t>185701</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>270054</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>339993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3207014</t>
+          <t>3203494</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3253555</t>
+          <t>3253639</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3336364</t>
+          <t>3340510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3388146</t>
+          <t>3390367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6561321</t>
+          <t>6561223</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6630328</t>
+          <t>6631162</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310599</t>
+          <t>314119</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309601</t>
+          <t>308442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311121</t>
+          <t>317038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278546</t>
+          <t>303061</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259977</t>
+          <t>291488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285553</t>
+          <t>309597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>589144</t>
+          <t>617180</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568820</t>
+          <t>602724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596396</t>
+          <t>624934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44353</t>
+          <t>42774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>34826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62882</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>491589</t>
+          <t>503201</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472884</t>
+          <t>486659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502209</t>
+          <t>513936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496514</t>
+          <t>520000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486834</t>
+          <t>507427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502685</t>
+          <t>527917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>988103</t>
+          <t>1023202</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966762</t>
+          <t>1005588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1001342</t>
+          <t>1037896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517237</t>
+          <t>529433</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517237</t>
+          <t>529433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517237</t>
+          <t>529433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512407</t>
+          <t>543289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512407</t>
+          <t>543289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512407</t>
+          <t>543289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029644</t>
+          <t>1072722</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029644</t>
+          <t>1072722</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029644</t>
+          <t>1072722</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>25923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39375</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>290882</t>
+          <t>290163</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281564</t>
+          <t>280825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297284</t>
+          <t>297061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>323794</t>
+          <t>328025</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314861</t>
+          <t>318497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329526</t>
+          <t>334678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>614676</t>
+          <t>618188</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602668</t>
+          <t>605900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624958</t>
+          <t>628297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>304806</t>
+          <t>304965</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>304806</t>
+          <t>304965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304806</t>
+          <t>304965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>337237</t>
+          <t>344420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>337237</t>
+          <t>344420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337237</t>
+          <t>344420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>642043</t>
+          <t>649385</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>642043</t>
+          <t>649385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>642043</t>
+          <t>649385</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -11839,27 +11839,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>311450</t>
+          <t>368534</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310680</t>
+          <t>360210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311776</t>
+          <t>372292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>469657</t>
+          <t>413142</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463991</t>
+          <t>406457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472397</t>
+          <t>416174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>781106</t>
+          <t>781676</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>776180</t>
+          <t>773119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783838</t>
+          <t>786353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311776</t>
+          <t>372292</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311776</t>
+          <t>372292</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311776</t>
+          <t>372292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473399</t>
+          <t>418095</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473399</t>
+          <t>418095</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473399</t>
+          <t>418095</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>785174</t>
+          <t>790387</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>785174</t>
+          <t>790387</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>785174</t>
+          <t>790387</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,22 +12104,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>256199</t>
+          <t>227145</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249889</t>
+          <t>224447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258282</t>
+          <t>228476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>434941</t>
+          <t>432809</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>427259</t>
+          <t>430015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>436933</t>
+          <t>434139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>263317</t>
+          <t>260618</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258452</t>
+          <t>251712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266295</t>
+          <t>265128</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>251464</t>
+          <t>256544</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245293</t>
+          <t>251014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254728</t>
+          <t>260380</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>514781</t>
+          <t>517163</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507811</t>
+          <t>508327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519491</t>
+          <t>523527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>50267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>53040</t>
+          <t>67725</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>52858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71743</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>592380</t>
+          <t>681117</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580691</t>
+          <t>667424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600589</t>
+          <t>690823</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>813312</t>
+          <t>725627</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>798220</t>
+          <t>713542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>829539</t>
+          <t>736042</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1405692</t>
+          <t>1406744</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1386989</t>
+          <t>1389727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1426330</t>
+          <t>1421611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>616626</t>
+          <t>710660</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>616626</t>
+          <t>710660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>616626</t>
+          <t>710660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>842106</t>
+          <t>763809</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>842106</t>
+          <t>763809</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>842106</t>
+          <t>763809</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1458732</t>
+          <t>1474469</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1458732</t>
+          <t>1474469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1458732</t>
+          <t>1474469</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>23866</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27971</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>915689</t>
+          <t>783789</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906040</t>
+          <t>773834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>920833</t>
+          <t>788404</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>697267</t>
+          <t>805589</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690551</t>
+          <t>797093</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701615</t>
+          <t>811533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1612957</t>
+          <t>1589378</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1602247</t>
+          <t>1577408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1621319</t>
+          <t>1597910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>923097</t>
+          <t>791841</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>923097</t>
+          <t>791841</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>923097</t>
+          <t>791841</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>707121</t>
+          <t>821403</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>707121</t>
+          <t>821403</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>707121</t>
+          <t>821403</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1630218</t>
+          <t>1613244</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1630218</t>
+          <t>1613244</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1630218</t>
+          <t>1613244</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56103</t>
+          <t>76391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>118263</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>101730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>144358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>216975</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>136957</t>
+          <t>189584</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201799</t>
+          <t>248382</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3354647</t>
+          <t>3407205</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3332304</t>
+          <t>3385307</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3376392</t>
+          <t>3427179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3586753</t>
+          <t>3579134</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3563730</t>
+          <t>3555387</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3608322</t>
+          <t>3598015</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6941400</t>
+          <t>6986341</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6908435</t>
+          <t>6954934</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6973277</t>
+          <t>7013732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
